--- a/reports/二级子公司D_利润表_2025-09.xlsx
+++ b/reports/二级子公司D_利润表_2025-09.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>86827798</v>
+        <v>88621057</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>84892935</v>
+        <v>84783219</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>739378293</v>
+        <v>739124021</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>293265</v>
+        <v>294241</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>2550158</v>
+        <v>2550149</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>253050</v>
+        <v>252803</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>2187386</v>
+        <v>2186704</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>208874</v>
+        <v>211048</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>1820909</v>
+        <v>1822925</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>190125</v>
+        <v>190118</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>1640914</v>
+        <v>1641090</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>104384</v>
+        <v>105609</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>910377</v>
+        <v>911846</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>84430</v>
+        <v>84392</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>729243</v>
+        <v>729460</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>85693670</v>
+        <v>87482846</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>83758807</v>
+        <v>83645008</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4724779</v>
+        <v>4714573</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>40993174</v>
+        <v>40996358</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>366785</v>
+        <v>365919</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>3187906</v>
+        <v>3187369</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>632342</v>
+        <v>626448</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>5468165</v>
+        <v>5462282</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>75216826</v>
+        <v>75147632</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>655551943</v>
+        <v>655338770</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1267366</v>
+        <v>1253352</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>10939244</v>
+        <v>10921767</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>417496</v>
+        <v>418471</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>3641489</v>
+        <v>3641007</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2111350</v>
+        <v>2097137</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>18231619</v>
+        <v>18209765</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>522776</v>
+        <v>525606</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>4552659</v>
+        <v>4554072</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1894889</v>
+        <v>1896553</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>16403450</v>
+        <v>16401124</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>39974</v>
+        <v>40207</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>359958</v>
+        <v>360259</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1140763</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>9846814</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>760315</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>6565331</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>56931564</v>
+        <v>61319361</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>51047947</v>
+        <v>51339523</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>50097619</v>
+        <v>50396901</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>436978518</v>
+        <v>437440572</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>950328</v>
+        <v>942622</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>8204420</v>
+        <v>8198840</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1881439</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>16391390</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>601325</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>5243604</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>375751</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>3276641</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>451283</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>3931858</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>339055</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>2949297</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>226566</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1966741</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>189280</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>1639552</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>887166</v>
+        <v>895835</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>7738212</v>
+        <v>7745371</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>686468</v>
+        <v>686140</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>5925512</v>
+        <v>5925009</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>522378</v>
+        <v>528146</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>4552288</v>
+        <v>4558825</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>4004403</v>
+        <v>4012325</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>34633432</v>
+        <v>34650488</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>149728</v>
+        <v>158164</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>1349678</v>
+        <v>1367690</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>319942</v>
+        <v>320669</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>2880054</v>
+        <v>2881640</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>360778</v>
+        <v>320669</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>3240655</v>
+        <v>2881640</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>39844</v>
+        <v>39887</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>359856</v>
+        <v>359914</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>161232</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>1457093</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>328821</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>2867502</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>107363</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>971024</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>80601</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>728314</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>134584</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1214136</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>472170</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>4097558</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>72130</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>648039</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>54216</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>486227</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>90493</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>810641</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>63378</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>567554</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>45246</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>405401</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>36143</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>324268</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>27048</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>243128</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>28762106</v>
+        <v>27306622</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>33014694</v>
+        <v>30438553</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>188066</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>1638987</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>44734</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>404628</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>69796</v>
+        <v>69592</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>629818</v>
+        <v>629365</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>28692310</v>
+        <v>27425096</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2486117</v>
+        <v>2493033</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>22486505</v>
+        <v>22484922</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>26206193</v>
+        <v>24932063</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>26206193</v>
+        <v>24932063</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>26206193</v>
+        <v>24932063</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>26206193</v>
+        <v>24932063</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>26206193</v>
+        <v>24932063</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
